--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260909.xlsx
@@ -638,139 +638,139 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>4,947,261,681</t>
+          <t>22,163,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>22,163,000</t>
+          <t>37,056,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>49,710,000</t>
+          <t>6,282,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,282,000</t>
+          <t>49,710,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>35,782,000</t>
+          <t>10,202,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10,202,000</t>
+          <t>4,168,628,656</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -814,24 +814,24 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>4,004,000</t>
+          <t>564,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,105 +843,105 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>27,131,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>564,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>26,264,000</t>
+          <t>35,990,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,846,000</t>
+          <t>4,004,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>34,858,000</t>
+          <t>6,846,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -968,73 +968,73 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>38,455,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,766,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>33,103,000</t>
+          <t>9,766,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,295,000</t>
+          <t>18,088,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,088,000</t>
+          <t>15,295,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,716,169,590</t>
+          <t>2,741,179,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1254,68 +1254,68 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>6,630,000</t>
+          <t>4,995,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,700,000</t>
+          <t>6,686,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,995,000</t>
+          <t>17,277,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>17,277,000</t>
+          <t>9,700,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>25,054,004</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1474,29 +1474,29 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1613,44 +1613,44 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>52,799,000</t>
+          <t>48,390,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>48,390,000</t>
+          <t>52,799,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>-232,568,792</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
